--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423898014371441</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>18960041</v>
+        <v>4514315</v>
       </c>
       <c r="L2" t="n">
-        <v>11279140</v>
+        <v>2519504</v>
       </c>
       <c r="M2" t="n">
-        <v>2723828</v>
+        <v>583337</v>
       </c>
       <c r="N2" t="n">
-        <v>99175</v>
+        <v>18285</v>
       </c>
       <c r="O2" t="n">
-        <v>1560520</v>
+        <v>345680</v>
       </c>
       <c r="P2" t="n">
-        <v>590445</v>
+        <v>132853</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999940395355225</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9242175221443176</v>
+        <v>0.876150906085968</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8399731516838074</v>
+        <v>0.754357635974884</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7972197532653809</v>
+        <v>0.6827589869499207</v>
       </c>
       <c r="U2" t="n">
-        <v>0.24952132999897</v>
+        <v>0.1895015090703964</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8297275304794312</v>
+        <v>0.7357820868492126</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9214559197425842</v>
+        <v>0.8486894369125366</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201873763595948</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>18960041</v>
+        <v>4514315</v>
       </c>
       <c r="E3" t="n">
-        <v>1294323</v>
+        <v>537447</v>
       </c>
       <c r="F3" t="n">
-        <v>9932</v>
+        <v>5646</v>
       </c>
       <c r="G3" t="n">
-        <v>1338</v>
+        <v>604</v>
       </c>
       <c r="H3" t="n">
-        <v>422</v>
+        <v>237</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>40278328</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>43843260</v>
+        <v>10719615</v>
       </c>
       <c r="L3" t="n">
-        <v>50405718</v>
+        <v>12311035</v>
       </c>
       <c r="M3" t="n">
-        <v>61235719</v>
+        <v>15210435</v>
       </c>
       <c r="N3" t="n">
-        <v>65008553</v>
+        <v>16248422</v>
       </c>
       <c r="O3" t="n">
-        <v>63306612</v>
+        <v>15782282</v>
       </c>
       <c r="P3" t="n">
-        <v>64840479</v>
+        <v>16198968</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9355551600456238</v>
+        <v>0.8924639821052551</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8603827357292175</v>
+        <v>0.7670806646347046</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7291833758354187</v>
+        <v>0.6242102980613708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2776758968830109</v>
+        <v>0.2045919895172119</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7660324573516846</v>
+        <v>0.6783559322357178</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7636460065841675</v>
+        <v>0.6871256828308105</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03188454573346271</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1451619</v>
+        <v>602703</v>
       </c>
       <c r="E4" t="n">
-        <v>11279140</v>
+        <v>2519504</v>
       </c>
       <c r="F4" t="n">
-        <v>356994</v>
+        <v>148575</v>
       </c>
       <c r="G4" t="n">
-        <v>8882</v>
+        <v>5170</v>
       </c>
       <c r="H4" t="n">
-        <v>12023</v>
+        <v>8042</v>
       </c>
       <c r="I4" t="n">
-        <v>785</v>
+        <v>542</v>
       </c>
       <c r="J4" t="n">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>1554654</v>
+        <v>638125</v>
       </c>
       <c r="L4" t="n">
-        <v>2148837</v>
+        <v>820429</v>
       </c>
       <c r="M4" t="n">
-        <v>692831</v>
+        <v>271045</v>
       </c>
       <c r="N4" t="n">
-        <v>298286</v>
+        <v>78205</v>
       </c>
       <c r="O4" t="n">
-        <v>320242</v>
+        <v>124133</v>
       </c>
       <c r="P4" t="n">
-        <v>50329</v>
+        <v>23686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999970197677612</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.929851770401001</v>
+        <v>0.884232223033905</v>
       </c>
       <c r="S4" t="n">
-        <v>0.850055456161499</v>
+        <v>0.7606658935546875</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7616852521896362</v>
+        <v>0.6521732211112976</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2628467977046967</v>
+        <v>0.1967578083276749</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7966088056564331</v>
+        <v>0.7059029936790466</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8351615071296692</v>
+        <v>0.759409487247467</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>67099</v>
+        <v>22394</v>
       </c>
       <c r="E5" t="n">
-        <v>753659</v>
+        <v>249870</v>
       </c>
       <c r="F5" t="n">
-        <v>2723828</v>
+        <v>583337</v>
       </c>
       <c r="G5" t="n">
-        <v>76501</v>
+        <v>23507</v>
       </c>
       <c r="H5" t="n">
-        <v>108829</v>
+        <v>51852</v>
       </c>
       <c r="I5" t="n">
-        <v>5530</v>
+        <v>3558</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1306045</v>
+        <v>543945</v>
       </c>
       <c r="L5" t="n">
-        <v>1830305</v>
+        <v>765032</v>
       </c>
       <c r="M5" t="n">
-        <v>1011622</v>
+        <v>351183</v>
       </c>
       <c r="N5" t="n">
-        <v>257986</v>
+        <v>71088</v>
       </c>
       <c r="O5" t="n">
-        <v>476626</v>
+        <v>163905</v>
       </c>
       <c r="P5" t="n">
-        <v>182747</v>
+        <v>60493</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999976754188538</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9564343094825745</v>
+        <v>0.9279928207397461</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9394014477729797</v>
+        <v>0.9034197926521301</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9740428328514099</v>
+        <v>0.9620962738990784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9915285110473633</v>
+        <v>0.9909056425094604</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9878644347190857</v>
+        <v>0.9824538230895996</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9964504837989807</v>
+        <v>0.9948721528053284</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>35818</v>
+        <v>12978</v>
       </c>
       <c r="E6" t="n">
-        <v>79382</v>
+        <v>18899</v>
       </c>
       <c r="F6" t="n">
-        <v>115112</v>
+        <v>29921</v>
       </c>
       <c r="G6" t="n">
-        <v>99175</v>
+        <v>18285</v>
       </c>
       <c r="H6" t="n">
-        <v>26348</v>
+        <v>8665</v>
       </c>
       <c r="I6" t="n">
-        <v>1311</v>
+        <v>619</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>20528</v>
+        <v>13622</v>
       </c>
       <c r="F7" t="n">
-        <v>206110</v>
+        <v>84125</v>
       </c>
       <c r="G7" t="n">
-        <v>207258</v>
+        <v>47177</v>
       </c>
       <c r="H7" t="n">
-        <v>1560520</v>
+        <v>345680</v>
       </c>
       <c r="I7" t="n">
-        <v>42681</v>
+        <v>18958</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>945</v>
+        <v>591</v>
       </c>
       <c r="F8" t="n">
-        <v>4683</v>
+        <v>2778</v>
       </c>
       <c r="G8" t="n">
-        <v>4307</v>
+        <v>1747</v>
       </c>
       <c r="H8" t="n">
-        <v>172620</v>
+        <v>55337</v>
       </c>
       <c r="I8" t="n">
-        <v>590445</v>
+        <v>132853</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
